--- a/Pakistan_poverty_analysis.xlsx
+++ b/Pakistan_poverty_analysis.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{503E46E7-12E0-4285-85D6-92419F0396CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9ABA3DC9-731A-4284-B6BE-25DD39162522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="16663" windowHeight="8743" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Govt Claim" sheetId="1" r:id="rId1"/>
     <sheet name="2. Multi-City Expenses" sheetId="2" r:id="rId2"/>
     <sheet name="3. National Gap Analysis" sheetId="3" r:id="rId3"/>
-    <sheet name="4. Elite Privilege Context" sheetId="4" r:id="rId4"/>
+    <sheet name="4. Elite Context (Unverified)" sheetId="4" r:id="rId4"/>
     <sheet name="5. Dashboard" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="122">
   <si>
     <t>PAKISTAN POVERTY LINE — OFFICIAL GOVERNMENT CLAIM</t>
   </si>
@@ -55,6 +55,9 @@
     <t>Daily Poverty Line (PKR)</t>
   </si>
   <si>
+    <t>At approx. 1 USD = 278 PKR</t>
+  </si>
+  <si>
     <t>Annual Poverty Line (PKR)</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t>USD equivalent / month</t>
   </si>
   <si>
+    <t xml:space="preserve">At ~1 USD = 278 PKR </t>
+  </si>
+  <si>
     <t>Source</t>
   </si>
   <si>
@@ -118,72 +124,108 @@
     <t>Higher in Karachi/Lahore; rural Sindh lower but rising</t>
   </si>
   <si>
+    <t>PBS HIES 2024-25 (Household Integrated Economic Survey), food &amp; beverage category average</t>
+  </si>
+  <si>
     <t>Rent — basic single room</t>
   </si>
   <si>
     <t>Karachi: North Nazimabad/Landhi. Lahore: Samanabad. RWP: Satellite Town</t>
   </si>
   <si>
+    <t>Zameen.com and OLX rental listings, mid-2025 sample (informal — not an official index)</t>
+  </si>
+  <si>
     <t>Electricity (summer peak)</t>
   </si>
   <si>
     <t>KESC/K-Electric (Karachi); LESCO (Lahore); IESCO (RWP); PESCO (KPK); HESCO/SEPCO (Sindh)</t>
   </si>
   <si>
+    <t>IESCO / LESCO / K-Electric / PESCO / HESCO published tariff schedules, summer slab</t>
+  </si>
+  <si>
     <t>Gas / Fuel</t>
   </si>
   <si>
     <t>Interior Sindh: no piped gas — LPG cylinder ~Rs. 3,000+ per month</t>
   </si>
   <si>
+    <t>OGRA LPG price notifications (interior Sindh) and SNGPL piped-gas tariff (other cities)</t>
+  </si>
+  <si>
     <t>Water</t>
   </si>
   <si>
     <t>KWSB (Karachi); WASA (Lahore/RWP); tanker supplements in all cities</t>
   </si>
   <si>
+    <t>WASA (Lahore/RWP) and KWSB (Karachi) published water tariffs; informal for tanker top-ups</t>
+  </si>
+  <si>
     <t>Transport (daily commute)</t>
   </si>
   <si>
     <t>Karachi: bus/rickshaw; Lahore: Metro/rickshaw; RWP: Metro Bus; rural: motorbike fuel</t>
   </si>
   <si>
+    <t>Local fare estimates — no single official source; verify against city transport authority rates</t>
+  </si>
+  <si>
     <t>Mobile / Internet (prepaid)</t>
   </si>
   <si>
     <t>Jazz/Telenor prepaid bundle; connectivity lower in interior</t>
   </si>
   <si>
+    <t>Jazz/Telenor publicly listed prepaid bundle prices</t>
+  </si>
+  <si>
     <t>Healthcare (basic OPD)</t>
   </si>
   <si>
     <t>Private GP costs higher in Karachi; rural relies on Basic Health Units (often dysfunctional)</t>
   </si>
   <si>
+    <t>Estimated from private GP consultation fee surveys — not an official source, verify locally</t>
+  </si>
+  <si>
     <t>Clothing / household (monthly share)</t>
   </si>
   <si>
     <t>Amortised over year; basic seasonal clothing</t>
   </si>
   <si>
+    <t>PBS HIES 2024-25 clothing/household category, amortised over the year</t>
+  </si>
+  <si>
     <t>Education (1 child, govt school fees/supplies)</t>
   </si>
   <si>
     <t>Optional — set 0 for single adult; significant for families</t>
   </si>
   <si>
+    <t>Estimated from public-school fee/supply cost surveys; verify with provincial education dept.</t>
+  </si>
+  <si>
     <t>Emergency buffer (8%)</t>
   </si>
   <si>
     <t>8% buffer for unplanned expenses</t>
   </si>
   <si>
+    <t>Calculated (8% of subtotal) — not independently sourced</t>
+  </si>
+  <si>
     <t>TOTAL MINIMUM MONTHLY COST</t>
   </si>
   <si>
     <t>Compare each city total vs govt poverty line of Rs. 8,483</t>
   </si>
   <si>
+    <t>Calculated (sum of rows above)</t>
+  </si>
+  <si>
     <t>⚠  All figures are estimates for illustrative purposes. Sources: PBS HIES 2024-25 | K-Electric/LESCO/IESCO/PESCO/HESCO tariffs | KWSB/WASA/WAPDA | Zameen.com/OLX (rent) | local market prices. Interior Sindh uses LPG (no SNGPL grid). Verify all before publication.</t>
   </si>
   <si>
@@ -238,10 +280,10 @@
     <t>KEY FINDING: A nationally uniform poverty threshold of Rs. 8,483 is absurd in Karachi where rent alone exceeds it. It is equally misleading in rural Sindh where cash income is irregular and LPG/transport costs are disproportionately high.</t>
   </si>
   <si>
-    <t>FOOD FOR THOUGHT — ELITE PRIVILEGES vs. POVERTY LINE</t>
-  </si>
-  <si>
-    <t>What Rs. 8,483/month looks like against state-funded elite perks</t>
+    <t>COMMENTARY — ELITE PRIVILEGES vs. POVERTY LINE (UNVERIFIED ESTIMATES)</t>
+  </si>
+  <si>
+    <t>Illustrative only — most figures below have no traceable official source. Do not present as audited data.</t>
   </si>
   <si>
     <t>Estimated Cost (PKR)</t>
@@ -250,6 +292,9 @@
     <t>Months of 'Poverty Line' Income</t>
   </si>
   <si>
+    <t>Confidence</t>
+  </si>
+  <si>
     <t>Govt poverty line (1 month)</t>
   </si>
   <si>
@@ -262,12 +307,18 @@
     <t>Approx. Karachi–Islamabad business class; verify on PIA.com</t>
   </si>
   <si>
+    <t>Verifiable — check current published fares on PIA.com</t>
+  </si>
+  <si>
     <t>Federal minister daily TA/DA allowance (est.)</t>
   </si>
   <si>
     <t>Approximate — actual figures vary; verify from Finance Division notifications</t>
   </si>
   <si>
+    <t>Unverified — no public source found; author estimate</t>
+  </si>
+  <si>
     <t>Government officer protocol car fuel (monthly est.)</t>
   </si>
   <si>
@@ -286,12 +337,18 @@
     <t>Includes salary, constituency allowance, fuel, medical; verify from NA website</t>
   </si>
   <si>
+    <t>Partially verifiable — NA website publishes salary/allowance structure, not a single total</t>
+  </si>
+  <si>
     <t>PM/CM motorcade operational cost per trip (est.)</t>
   </si>
   <si>
     <t>Multiple protocol vehicles, security, fuel; estimate only — no official disclosure</t>
   </si>
   <si>
+    <t>Unverified — no official disclosure exists for this figure</t>
+  </si>
+  <si>
     <t>Annual cost of one Grade-22 officer perks (est.)</t>
   </si>
   <si>
@@ -338,12 +395,6 @@
   </si>
   <si>
     <t>⚠  All figures estimated. Red bars = Rs. 8,483 poverty line. Verify against PBS HIES 2024-25 | Utility company tariffs | Zameen.com | Economic Survey 2024-25.</t>
-  </si>
-  <si>
-    <t>At approx. 1 USD = 278 PKR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">At ~1 USD = 278 PKR </t>
   </si>
 </sst>
 </file>
@@ -396,6 +447,22 @@
       <sz val="9"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF00008B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -526,21 +593,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF00008B"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF555555"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="18">
@@ -674,15 +726,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -691,7 +743,7 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -706,7 +758,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -733,8 +785,20 @@
     <xf numFmtId="3" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -742,91 +806,100 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="12" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="14" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="16" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -838,68 +911,56 @@
     <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="21" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="22" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="23" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="25" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="25" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -999,7 +1060,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
+              <a:defRPr lang="en-US" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1093,7 +1154,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -1146,7 +1207,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0E01-4451-8615-7A0D62C09188}"/>
+              <c16:uniqueId val="{00000000-18A2-4BA8-9CE3-27602369795D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1210,7 +1271,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -1263,7 +1324,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0E01-4451-8615-7A0D62C09188}"/>
+              <c16:uniqueId val="{00000001-18A2-4BA8-9CE3-27602369795D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1276,11 +1337,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="10609685"/>
-        <c:axId val="75359485"/>
+        <c:axId val="13253256"/>
+        <c:axId val="68857631"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="10609685"/>
+        <c:axId val="13253256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1293,7 +1354,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                  <a:defRPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1347,7 +1408,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75359485"/>
+        <c:crossAx val="68857631"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1355,7 +1416,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="75359485"/>
+        <c:axId val="68857631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1378,7 +1439,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                  <a:defRPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1432,7 +1493,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10609685"/>
+        <c:crossAx val="13253256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1502,9 +1563,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>25200</xdr:colOff>
+      <xdr:colOff>24840</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>86040</xdr:rowOff>
+      <xdr:rowOff>85680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1712,29 +1773,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.61328125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
     </row>
-    <row r="2" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
     </row>
-    <row r="3" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
@@ -1745,7 +1806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
         <v>5</v>
       </c>
@@ -1756,7 +1817,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="18" t="s">
         <v>7</v>
       </c>
@@ -1764,60 +1825,60 @@
         <f>B5/30</f>
         <v>282.76666666666665</v>
       </c>
-      <c r="C6" s="75" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="16">
         <f>B5*12</f>
         <v>101796</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="20">
+        <v>11</v>
+      </c>
+      <c r="B8" s="21">
         <f>B5/278</f>
         <v>30.514388489208635</v>
       </c>
-      <c r="C8" s="76" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="73" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>14</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="21" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
@@ -1835,17 +1896,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultColWidth="8.61328125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1854,9 +1916,9 @@
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
     </row>
-    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -1865,320 +1927,359 @@
       <c r="F2" s="9"/>
       <c r="G2" s="9"/>
     </row>
-    <row r="3" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="22" t="s">
+    <row r="3" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="B4" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="C4" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="D4" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="E4" s="26" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="23" t="s">
+      <c r="F4" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="24">
+      <c r="G4" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="29">
         <v>10000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="29">
         <v>9000</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="29">
         <v>8500</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="29">
         <v>8000</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="29">
         <v>6500</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="27">
+      <c r="G5" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="33">
         <v>18000</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="33">
         <v>12000</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="33">
         <v>8000</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="33">
         <v>7000</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="33">
         <v>3000</v>
       </c>
-      <c r="G6" s="28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="24">
+      <c r="G6" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="29">
         <v>6000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="29">
         <v>5000</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="29">
         <v>3500</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="29">
         <v>2500</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="29">
         <v>4000</v>
       </c>
-      <c r="G7" s="25" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="27">
+      <c r="G7" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="33">
         <v>1200</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="33">
         <v>1000</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="33">
         <v>600</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="33">
         <v>800</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="33">
         <v>1500</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="24">
+      <c r="G8" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="29">
         <v>1000</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="29">
         <v>700</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="29">
         <v>500</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="29">
         <v>600</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="29">
         <v>800</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="27">
+      <c r="G9" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="33">
         <v>4000</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="33">
         <v>3000</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="33">
         <v>2000</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="33">
         <v>2500</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="33">
         <v>1500</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="G10" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="29">
         <v>1200</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="29">
         <v>1000</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="29">
         <v>800</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="29">
         <v>800</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="29">
         <v>700</v>
       </c>
-      <c r="G11" s="25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="27">
+      <c r="G11" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="33">
         <v>2000</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="33">
         <v>1500</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="33">
         <v>500</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="33">
         <v>800</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="33">
         <v>600</v>
       </c>
-      <c r="G12" s="28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="24">
+      <c r="G12" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="29">
         <v>1500</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="29">
         <v>1200</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="29">
         <v>700</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="29">
         <v>800</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="29">
         <v>600</v>
       </c>
-      <c r="G13" s="25" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="27">
+      <c r="G13" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="33">
         <v>1500</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="33">
         <v>1200</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="33">
         <v>1000</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="33">
         <v>800</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="33">
         <v>500</v>
       </c>
-      <c r="G14" s="28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="29">
+      <c r="G14" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="35">
         <f>SUM(B5:B14)*0.08</f>
         <v>3712</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="35">
         <f>SUM(C5:C14)*0.08</f>
         <v>2848</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="35">
         <f>SUM(D5:D14)*0.08</f>
         <v>2088</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="35">
         <f>SUM(E5:E14)*0.08</f>
         <v>1968</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="35">
         <f>SUM(F5:F14)*0.08</f>
         <v>1576</v>
       </c>
-      <c r="G15" s="25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="31">
+      <c r="G15" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="37">
         <f>SUM(B5:B15)</f>
         <v>50112</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="37">
         <f>SUM(C5:C15)</f>
         <v>38448</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="37">
         <f>SUM(D5:D15)</f>
         <v>28188</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="37">
         <f>SUM(E5:E15)</f>
         <v>26568</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="37">
         <f>SUM(F5:F15)</f>
         <v>21276</v>
       </c>
-      <c r="G16" s="32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G16" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="11" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -2201,16 +2302,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.61328125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -2219,9 +2320,9 @@
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
     </row>
-    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -2230,197 +2331,197 @@
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
     </row>
-    <row r="3" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="33" t="s">
+    <row r="3" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="C4" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="D4" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="34">
+        <v>70</v>
+      </c>
+      <c r="B5" s="41">
         <v>8483</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="41">
         <v>8483</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="41">
         <v>8483</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="41">
         <v>8483</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="41">
         <v>8483</v>
       </c>
-      <c r="G5" s="35" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="37">
+      <c r="G5" s="42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="44">
         <f>'2. Multi-City Expenses'!B16</f>
         <v>50112</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="44">
         <f>'2. Multi-City Expenses'!C16</f>
         <v>38448</v>
       </c>
-      <c r="D6" s="37">
+      <c r="D6" s="44">
         <f>'2. Multi-City Expenses'!D16</f>
         <v>28188</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="44">
         <f>'2. Multi-City Expenses'!E16</f>
         <v>26568</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="44">
         <f>'2. Multi-City Expenses'!F16</f>
         <v>21276</v>
       </c>
-      <c r="G6" s="38" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="40">
+      <c r="G6" s="45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="47">
         <f>B6-B5</f>
         <v>41629</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="47">
         <f>C6-C5</f>
         <v>29965</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="47">
         <f>D6-D5</f>
         <v>19705</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="47">
         <f>E6-E5</f>
         <v>18085</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="47">
         <f>F6-F5</f>
         <v>12793</v>
       </c>
-      <c r="G7" s="41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="42">
+      <c r="G7" s="48" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="49">
         <f>(B6-B5)/B5</f>
         <v>4.9073440999646349</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="49">
         <f>(C6-C5)/C5</f>
         <v>3.532358835317694</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="49">
         <f>(D6-D5)/D5</f>
         <v>2.3228810562301074</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="49">
         <f>(E6-E5)/E5</f>
         <v>2.1319108805846989</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="49">
         <f>(F6-F5)/F5</f>
         <v>1.5080749734763645</v>
       </c>
-      <c r="G8" s="38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G8" s="45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="43">
+        <v>78</v>
+      </c>
+      <c r="B9" s="50">
         <f>B5/B6</f>
         <v>0.1692808109833972</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="50">
         <f>C5/C6</f>
         <v>0.22063566375364127</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="50">
         <f>D5/D6</f>
         <v>0.30094366397048389</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="50">
         <f>E5/E6</f>
         <v>0.31929388738331826</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="50">
         <f>F5/F6</f>
         <v>0.39871216394059034</v>
       </c>
-      <c r="G9" s="35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="44">
+      <c r="G9" s="42" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="51">
         <f>B5/B6*12</f>
         <v>2.0313697318007664</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="51">
         <f>C5/C6*12</f>
         <v>2.6476279650436951</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="51">
         <f>D5/D6*12</f>
         <v>3.6113239676458067</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="51">
         <f>E5/E6*12</f>
         <v>3.8315266485998194</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F10" s="51">
         <f>F5/F6*12</f>
         <v>4.7845459672870838</v>
       </c>
-      <c r="G10" s="38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G10" s="45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -2443,16 +2544,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.61328125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2461,9 +2563,9 @@
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
     </row>
-    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -2472,169 +2574,199 @@
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
     </row>
-    <row r="3" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="45" t="s">
+    <row r="3" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="45" t="s">
+      <c r="B4" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="D4" s="52" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="27" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="24">
+        <v>88</v>
+      </c>
+      <c r="B5" s="29">
         <v>8483</v>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="53">
         <f t="shared" ref="C5:C13" si="0">B5/8483</f>
         <v>1</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="47" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="48">
+      <c r="D5" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="55">
         <v>65000</v>
       </c>
-      <c r="C6" s="49">
+      <c r="C6" s="56">
         <f t="shared" si="0"/>
         <v>7.6623835907108333</v>
       </c>
-      <c r="D6" s="50" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="24">
+      <c r="D6" s="57" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="29">
         <v>25000</v>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="58">
         <f t="shared" si="0"/>
         <v>2.947070611811859</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="47" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="48">
+      <c r="D7" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="55">
         <v>40000</v>
       </c>
-      <c r="C8" s="49">
+      <c r="C8" s="56">
         <f t="shared" si="0"/>
         <v>4.7153129788989743</v>
       </c>
-      <c r="D8" s="50" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="24">
+      <c r="D8" s="57" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="29">
         <v>15000</v>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="58">
         <f t="shared" si="0"/>
         <v>1.7682423670871155</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="48">
+      <c r="D9" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="55">
         <v>250000</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="56">
         <f t="shared" si="0"/>
         <v>29.470706118118589</v>
       </c>
-      <c r="D10" s="50" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="24">
+      <c r="D10" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="29">
         <v>500000</v>
       </c>
-      <c r="C11" s="51">
+      <c r="C11" s="58">
         <f t="shared" si="0"/>
         <v>58.941412236237177</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="B12" s="48">
+      <c r="D11" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="54" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="55">
         <v>2400000</v>
       </c>
-      <c r="C12" s="49">
+      <c r="C12" s="56">
         <f t="shared" si="0"/>
         <v>282.91877873393844</v>
       </c>
-      <c r="D12" s="50" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="24">
+      <c r="D12" s="57" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="29">
         <v>1200000</v>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="58">
         <f t="shared" si="0"/>
         <v>141.45938936696922</v>
       </c>
-      <c r="D13" s="25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="15" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D13" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
     </row>
-    <row r="16" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="17" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="11" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -2655,7 +2787,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:G47"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.61328125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2663,9 +2795,9 @@
     <col min="8" max="8" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B1" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2673,9 +2805,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -2683,161 +2815,161 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="45" t="s">
+    <row r="3" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="C4" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="54" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="55">
+      <c r="D4" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="62">
         <f>'2. Multi-City Expenses'!B16</f>
         <v>50112</v>
       </c>
-      <c r="C5" s="56">
+      <c r="C5" s="63">
         <f>'2. Multi-City Expenses'!C16</f>
         <v>38448</v>
       </c>
-      <c r="D5" s="57">
+      <c r="D5" s="64">
         <f>'2. Multi-City Expenses'!D16</f>
         <v>28188</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="65">
         <f>'2. Multi-City Expenses'!E16</f>
         <v>26568</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="66">
         <f>'2. Multi-City Expenses'!F16</f>
         <v>21276</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="60">
+    <row r="6" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="67">
         <f>'3. National Gap Analysis'!B7</f>
         <v>41629</v>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="68">
         <f>'3. National Gap Analysis'!C7</f>
         <v>29965</v>
       </c>
-      <c r="D6" s="62">
+      <c r="D6" s="69">
         <f>'3. National Gap Analysis'!D7</f>
         <v>19705</v>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="70">
         <f>'3. National Gap Analysis'!E7</f>
         <v>18085</v>
       </c>
-      <c r="F6" s="64">
+      <c r="F6" s="71">
         <f>'3. National Gap Analysis'!F7</f>
         <v>12793</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="65" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="D7" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="68" t="s">
-        <v>96</v>
-      </c>
-      <c r="F7" s="69" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="70" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" s="70" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" s="70" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="72">
+    <row r="7" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="72" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="75" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="76" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" ht="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="2:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="77" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="77" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="78" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="79">
         <f>'2. Multi-City Expenses'!B16</f>
         <v>50112</v>
       </c>
-      <c r="D10" s="72">
+      <c r="D10" s="79">
         <v>8483</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="72">
+    <row r="11" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="79">
         <f>'2. Multi-City Expenses'!C16</f>
         <v>38448</v>
       </c>
-      <c r="D11" s="72">
+      <c r="D11" s="79">
         <v>8483</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="71" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="72">
+    <row r="12" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="78" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="79">
         <f>'2. Multi-City Expenses'!D16</f>
         <v>28188</v>
       </c>
-      <c r="D12" s="72">
+      <c r="D12" s="79">
         <v>8483</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="71" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="72">
+    <row r="13" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="79">
         <f>'2. Multi-City Expenses'!E16</f>
         <v>26568</v>
       </c>
-      <c r="D13" s="72">
+      <c r="D13" s="79">
         <v>8483</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="71" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="72">
+    <row r="14" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="78" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" s="79">
         <f>'2. Multi-City Expenses'!F16</f>
         <v>21276</v>
       </c>
-      <c r="D14" s="72">
+      <c r="D14" s="79">
         <v>8483</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="2:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:7" ht="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" spans="2:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B47" s="11" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
